--- a/research/traditional_assets/database/data/new_zealand/new_zealand_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_electrical_equipment.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.096</v>
+        <v>0.102</v>
       </c>
       <c r="G2">
-        <v>-0.01371951219512196</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="H2">
-        <v>-0.05640243902439025</v>
+        <v>0.01127450980392157</v>
       </c>
       <c r="I2">
-        <v>-0.0226829268292683</v>
+        <v>-0.03480392156862745</v>
       </c>
       <c r="J2">
-        <v>-0.0226829268292683</v>
+        <v>-0.03480392156862745</v>
       </c>
       <c r="K2">
-        <v>-0.528</v>
+        <v>1.83</v>
       </c>
       <c r="L2">
-        <v>-0.01609756097560976</v>
+        <v>0.0448529411764706</v>
       </c>
       <c r="M2">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.000264026402640264</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.0303030303030303</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0.016</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4.29</v>
+        <v>3.01</v>
       </c>
       <c r="V2">
-        <v>0.07079207920792079</v>
+        <v>0.09465408805031446</v>
       </c>
       <c r="W2">
-        <v>-0.06675094816687738</v>
+        <v>0.1678899082568807</v>
       </c>
       <c r="X2">
-        <v>0.05909216456659307</v>
+        <v>0.1061407498551275</v>
       </c>
       <c r="Y2">
-        <v>-0.1258431127334705</v>
+        <v>0.06174915840175327</v>
       </c>
       <c r="Z2">
-        <v>5.29886914378029</v>
+        <v>6.915254237288135</v>
       </c>
       <c r="AA2">
-        <v>-0.1201938610662358</v>
+        <v>-0.2406779661016949</v>
       </c>
       <c r="AB2">
-        <v>0.05816339469603699</v>
+        <v>0.1034116961819377</v>
       </c>
       <c r="AC2">
-        <v>-0.1783572557622728</v>
+        <v>-0.3440896622836326</v>
       </c>
       <c r="AD2">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG2">
-        <v>-2.81</v>
+        <v>-1.65</v>
       </c>
       <c r="AH2">
-        <v>0.02384020618556701</v>
+        <v>0.04101326899879373</v>
       </c>
       <c r="AI2">
-        <v>0.1195476575121163</v>
+        <v>0.1002949852507375</v>
       </c>
       <c r="AJ2">
-        <v>-0.04862432946876622</v>
+        <v>-0.05472636815920397</v>
       </c>
       <c r="AK2">
-        <v>-0.3473423980222497</v>
+        <v>-0.1563981042654028</v>
       </c>
       <c r="AL2">
-        <v>0.182</v>
+        <v>0.152</v>
       </c>
       <c r="AM2">
-        <v>0.173</v>
+        <v>0.128</v>
       </c>
       <c r="AN2">
-        <v>-4.868421052631579</v>
+        <v>-1.236363636363636</v>
       </c>
       <c r="AO2">
-        <v>-4.087912087912088</v>
+        <v>-9.342105263157894</v>
       </c>
       <c r="AP2">
-        <v>9.243421052631579</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>-4.300578034682081</v>
+        <v>-11.09375</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wellington Drive Technologies Limited (NZSE:WDT)</t>
+          <t>AoFrio Limited (NZSE:AOF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.096</v>
+        <v>0.102</v>
       </c>
       <c r="G3">
-        <v>-0.01371951219512196</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="H3">
-        <v>-0.05640243902439025</v>
+        <v>0.01127450980392157</v>
       </c>
       <c r="I3">
-        <v>-0.0226829268292683</v>
+        <v>-0.03480392156862745</v>
       </c>
       <c r="J3">
-        <v>-0.0226829268292683</v>
+        <v>-0.03480392156862745</v>
       </c>
       <c r="K3">
-        <v>-0.528</v>
+        <v>1.83</v>
       </c>
       <c r="L3">
-        <v>-0.01609756097560976</v>
+        <v>0.0448529411764706</v>
       </c>
       <c r="M3">
-        <v>0.016</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.000264026402640264</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.0303030303030303</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,82 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.016</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4.29</v>
+        <v>3.01</v>
       </c>
       <c r="V3">
-        <v>0.07079207920792079</v>
+        <v>0.09465408805031446</v>
       </c>
       <c r="W3">
-        <v>-0.06675094816687738</v>
+        <v>0.1678899082568807</v>
       </c>
       <c r="X3">
-        <v>0.05909216456659307</v>
+        <v>0.1061407498551275</v>
       </c>
       <c r="Y3">
-        <v>-0.1258431127334705</v>
+        <v>0.06174915840175327</v>
       </c>
       <c r="Z3">
-        <v>5.29886914378029</v>
+        <v>6.915254237288135</v>
       </c>
       <c r="AA3">
-        <v>-0.1201938610662358</v>
+        <v>-0.2406779661016949</v>
       </c>
       <c r="AB3">
-        <v>0.05816339469603699</v>
+        <v>0.1034116961819377</v>
       </c>
       <c r="AC3">
-        <v>-0.1783572557622728</v>
+        <v>-0.3440896622836326</v>
       </c>
       <c r="AD3">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG3">
-        <v>-2.81</v>
+        <v>-1.65</v>
       </c>
       <c r="AH3">
-        <v>0.02384020618556701</v>
+        <v>0.04101326899879373</v>
       </c>
       <c r="AI3">
-        <v>0.1195476575121163</v>
+        <v>0.1002949852507375</v>
       </c>
       <c r="AJ3">
-        <v>-0.04862432946876622</v>
+        <v>-0.05472636815920397</v>
       </c>
       <c r="AK3">
-        <v>-0.3473423980222497</v>
+        <v>-0.1563981042654028</v>
       </c>
       <c r="AL3">
-        <v>0.182</v>
+        <v>0.152</v>
       </c>
       <c r="AM3">
-        <v>0.173</v>
+        <v>0.128</v>
       </c>
       <c r="AN3">
-        <v>-4.868421052631579</v>
+        <v>-1.236363636363636</v>
       </c>
       <c r="AO3">
-        <v>-4.087912087912088</v>
+        <v>-9.342105263157894</v>
       </c>
       <c r="AP3">
-        <v>9.243421052631579</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>-4.300578034682081</v>
+        <v>-11.09375</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_electrical_equipment.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.102</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="G2">
-        <v>0.04705882352941176</v>
+        <v>0.01707207207207207</v>
       </c>
       <c r="H2">
-        <v>0.01127450980392157</v>
+        <v>-0.007927927927927928</v>
       </c>
       <c r="I2">
-        <v>-0.03480392156862745</v>
+        <v>-0.02905405405405406</v>
       </c>
       <c r="J2">
-        <v>-0.03480392156862745</v>
+        <v>-0.02905405405405406</v>
       </c>
       <c r="K2">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="L2">
-        <v>0.0448529411764706</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.008597560975609757</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.09399999999999999</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,79 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.141</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>3.01</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>0.09465408805031446</v>
+        <v>0.09390243902439026</v>
       </c>
       <c r="W2">
-        <v>0.1678899082568807</v>
+        <v>0.1229508196721312</v>
       </c>
       <c r="X2">
-        <v>0.1061407498551275</v>
+        <v>0.1073625950823212</v>
       </c>
       <c r="Y2">
-        <v>0.06174915840175327</v>
+        <v>0.01558822458980995</v>
       </c>
       <c r="Z2">
-        <v>6.915254237288135</v>
+        <v>5.211267605633803</v>
       </c>
       <c r="AA2">
-        <v>-0.2406779661016949</v>
+        <v>-0.1514084507042254</v>
       </c>
       <c r="AB2">
-        <v>0.1034116961819377</v>
+        <v>0.08405021649019083</v>
       </c>
       <c r="AC2">
-        <v>-0.3440896622836326</v>
+        <v>-0.2354586671944162</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>8.06</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.36</v>
+        <v>8.06</v>
       </c>
       <c r="AG2">
-        <v>-1.65</v>
+        <v>6.52</v>
       </c>
       <c r="AH2">
-        <v>0.04101326899879373</v>
+        <v>0.3295175797219951</v>
       </c>
       <c r="AI2">
-        <v>0.1002949852507375</v>
+        <v>0.3863854266538831</v>
       </c>
       <c r="AJ2">
-        <v>-0.05472636815920397</v>
+        <v>0.2844677137870856</v>
       </c>
       <c r="AK2">
-        <v>-0.1563981042654028</v>
+        <v>0.3374741200828157</v>
       </c>
       <c r="AL2">
-        <v>0.152</v>
+        <v>0.494</v>
       </c>
       <c r="AM2">
-        <v>0.128</v>
+        <v>0.459</v>
       </c>
       <c r="AN2">
-        <v>-1.236363636363636</v>
+        <v>-9.025755879059352</v>
       </c>
       <c r="AO2">
-        <v>-9.342105263157894</v>
+        <v>-2.611336032388664</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>-7.301231802911534</v>
       </c>
       <c r="AQ2">
-        <v>-11.09375</v>
+        <v>-2.81045751633987</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.102</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="G3">
-        <v>0.04705882352941176</v>
+        <v>0.01707207207207207</v>
       </c>
       <c r="H3">
-        <v>0.01127450980392157</v>
+        <v>-0.007927927927927928</v>
       </c>
       <c r="I3">
-        <v>-0.03480392156862745</v>
+        <v>-0.02905405405405406</v>
       </c>
       <c r="J3">
-        <v>-0.03480392156862745</v>
+        <v>-0.02905405405405406</v>
       </c>
       <c r="K3">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="L3">
-        <v>0.0448529411764706</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.141</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.008597560975609757</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.09399999999999999</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +758,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.141</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>3.01</v>
+        <v>1.54</v>
       </c>
       <c r="V3">
-        <v>0.09465408805031446</v>
+        <v>0.09390243902439026</v>
       </c>
       <c r="W3">
-        <v>0.1678899082568807</v>
+        <v>0.1229508196721312</v>
       </c>
       <c r="X3">
-        <v>0.1061407498551275</v>
+        <v>0.1073625950823212</v>
       </c>
       <c r="Y3">
-        <v>0.06174915840175327</v>
+        <v>0.01558822458980995</v>
       </c>
       <c r="Z3">
-        <v>6.915254237288135</v>
+        <v>5.211267605633803</v>
       </c>
       <c r="AA3">
-        <v>-0.2406779661016949</v>
+        <v>-0.1514084507042254</v>
       </c>
       <c r="AB3">
-        <v>0.1034116961819377</v>
+        <v>0.08405021649019083</v>
       </c>
       <c r="AC3">
-        <v>-0.3440896622836326</v>
+        <v>-0.2354586671944162</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>8.06</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.36</v>
+        <v>8.06</v>
       </c>
       <c r="AG3">
-        <v>-1.65</v>
+        <v>6.52</v>
       </c>
       <c r="AH3">
-        <v>0.04101326899879373</v>
+        <v>0.3295175797219951</v>
       </c>
       <c r="AI3">
-        <v>0.1002949852507375</v>
+        <v>0.3863854266538831</v>
       </c>
       <c r="AJ3">
-        <v>-0.05472636815920397</v>
+        <v>0.2844677137870856</v>
       </c>
       <c r="AK3">
-        <v>-0.1563981042654028</v>
+        <v>0.3374741200828157</v>
       </c>
       <c r="AL3">
-        <v>0.152</v>
+        <v>0.494</v>
       </c>
       <c r="AM3">
-        <v>0.128</v>
+        <v>0.459</v>
       </c>
       <c r="AN3">
-        <v>-1.236363636363636</v>
+        <v>-9.025755879059352</v>
       </c>
       <c r="AO3">
-        <v>-9.342105263157894</v>
+        <v>-2.611336032388664</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>-7.301231802911534</v>
       </c>
       <c r="AQ3">
-        <v>-11.09375</v>
+        <v>-2.81045751633987</v>
       </c>
     </row>
   </sheetData>
